--- a/data/test_set.xlsx
+++ b/data/test_set.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20752" windowHeight="9105"/>
+    <workbookView windowWidth="20752" windowHeight="9555"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6986,7 +6986,7 @@
     <t>外卖订单晒没看出来？少吃节用，这个女的一直要他钱，骗他所有，最后不要他，还有黑子洗，无语</t>
   </si>
   <si>
-    <t>漂白水都洗不白了，不喜欢他，为了钱跟他老公这样那样，怎么聊天记录这里没有？</t>
+    <t>漂白水都洗不白了，不喜欢她，为了钱跟她老公这样那样，怎么聊天记录这里没有？</t>
   </si>
   <si>
     <t>一边装，一边收钱一直要钱什么意思？好一个装逼</t>
